--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>78.44130765131253</v>
+        <v>12.74671249333829</v>
       </c>
       <c r="D2" t="n">
-        <v>51.97497556670892</v>
+        <v>8.445933529590199</v>
       </c>
       <c r="E2" t="n">
-        <v>26.94495865176151</v>
+        <v>4.378555780911245</v>
       </c>
       <c r="F2" t="n">
-        <v>15.34614680448512</v>
+        <v>2.493748855728833</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.42914183249896</v>
+        <v>9.33223554778108</v>
       </c>
       <c r="D3" t="n">
-        <v>10.3257109867656</v>
+        <v>1.67792803534941</v>
       </c>
       <c r="E3" t="n">
-        <v>26.94495865176151</v>
+        <v>4.378555780911245</v>
       </c>
       <c r="F3" t="n">
-        <v>15.34614680448512</v>
+        <v>2.493748855728833</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>74.58682946952163</v>
+        <v>12.12035978879727</v>
       </c>
       <c r="D4" t="n">
-        <v>31.13783473247065</v>
+        <v>5.059898144026482</v>
       </c>
       <c r="E4" t="n">
-        <v>26.94495865176151</v>
+        <v>4.378555780911245</v>
       </c>
       <c r="F4" t="n">
-        <v>15.34614680448512</v>
+        <v>2.493748855728833</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.11419734121078</v>
+        <v>4.081057067946751</v>
       </c>
       <c r="D5" t="n">
-        <v>25.27152547829276</v>
+        <v>4.106622890222574</v>
       </c>
       <c r="E5" t="n">
-        <v>26.94495865176151</v>
+        <v>4.378555780911245</v>
       </c>
       <c r="F5" t="n">
-        <v>15.34614680448512</v>
+        <v>2.493748855728833</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.69314165545603</v>
+        <v>1.737635519011604</v>
       </c>
       <c r="D6" t="n">
-        <v>10.82589488217949</v>
+        <v>1.759207918354167</v>
       </c>
       <c r="E6" t="n">
-        <v>26.94495865176151</v>
+        <v>4.378555780911245</v>
       </c>
       <c r="F6" t="n">
-        <v>15.34614680448512</v>
+        <v>2.493748855728833</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
